--- a/output/pdf_financials_xlsx/MSCL.xlsx
+++ b/output/pdf_financials_xlsx/MSCL.xlsx
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004971</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007986</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.02063</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.57853</v>
+        <v>-1.583501</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-15.505652</v>
+        <v>-15.513638</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.316818</v>
+        <v>-11.337448</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.578108</v>
+        <v>-1.583079</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-15.339967</v>
+        <v>-15.347953</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.983818</v>
+        <v>-11.004448</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E290" s="5" t="n">

--- a/output/pdf_financials_xlsx/MSCL.xlsx
+++ b/output/pdf_financials_xlsx/MSCL.xlsx
@@ -1180,10 +1180,10 @@
         <v>0.000422</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.165685</v>
+        <v>0.164945</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.333</v>
+        <v>0.333323</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="29">
@@ -1207,10 +1207,10 @@
         <v>-1.583079</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-15.347953</v>
+        <v>-15.348693</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.004448</v>
+        <v>-11.004125</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-21.637</v>
+        <v>-21.622</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-26.061</v>
+        <v>-26.057</v>
       </c>
     </row>
     <row r="30">
@@ -2998,19 +2998,19 @@
         <v>0.000422</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.165685</v>
+        <v>0.164945</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="101">
@@ -7476,7 +7476,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -9320,7 +9324,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10462,7 +10466,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -16730,7 +16734,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">

--- a/output/pdf_financials_xlsx/MSCL.xlsx
+++ b/output/pdf_financials_xlsx/MSCL.xlsx
@@ -2107,16 +2107,16 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.466</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>2.063</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.772</v>
       </c>
     </row>
     <row r="65">
@@ -2176,19 +2176,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.091486</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.975189</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.364</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>2.584</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>2.187</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -3273,10 +3273,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007246</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>-0.018</v>
@@ -3870,10 +3870,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007246</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>-0.018</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-5.035155</v>
+        <v>-5.042401</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-5.719</v>
+        <v>-5.722</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-12.766</v>
@@ -10244,7 +10244,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
